--- a/data/markers.xlsx
+++ b/data/markers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PierrickUro\Documents\SLMT\slmtwebmap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AFDF277-62F4-4689-9BF4-CB4C30673281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB5CE182-D4B0-46E6-B7D2-2A3EC1DF128F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="432">
   <si>
     <t>id</t>
   </si>
@@ -1341,6 +1341,39 @@
   <si>
     <t>override</t>
   </si>
+  <si>
+    <t>52.210500678757676, -9.094416628022241</t>
+  </si>
+  <si>
+    <t>52.262754620845044, -9.232563881978308</t>
+  </si>
+  <si>
+    <t>52.071688450813376, -9.443847914430686</t>
+  </si>
+  <si>
+    <t>52.37186786279594, -9.313780935756268</t>
+  </si>
+  <si>
+    <t>52.26693781107842, -9.470387724679604</t>
+  </si>
+  <si>
+    <t>52.25423147433303, -9.406584937620872</t>
+  </si>
+  <si>
+    <t>52.21343400674858, -9.29287537059192</t>
+  </si>
+  <si>
+    <t>52.215670981642184, -9.393566706779227</t>
+  </si>
+  <si>
+    <t>52.11601343303832, -9.361063317919415</t>
+  </si>
+  <si>
+    <t>52.31132780517801, -9.304468109935828</t>
+  </si>
+  <si>
+    <t>REMOVE</t>
+  </si>
 </sst>
 </file>
 
@@ -1350,7 +1383,7 @@
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.0000000"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1454,8 +1487,14 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1465,6 +1504,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1561,9 +1606,6 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1574,7 +1616,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1586,6 +1627,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1881,7 +1928,7 @@
     <col min="8" max="8" width="14.54296875" customWidth="1"/>
     <col min="9" max="10" width="18.6328125" style="7" customWidth="1"/>
     <col min="12" max="12" width="33.1796875" customWidth="1"/>
-    <col min="14" max="14" width="31.1796875" style="33" customWidth="1"/>
+    <col min="14" max="14" width="31.1796875" customWidth="1"/>
     <col min="15" max="15" width="61" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1925,7 +1972,7 @@
       <c r="M1" t="s">
         <v>230</v>
       </c>
-      <c r="N1" s="33" t="s">
+      <c r="N1" t="s">
         <v>5</v>
       </c>
       <c r="O1" s="7" t="s">
@@ -2413,7 +2460,7 @@
       <c r="C18" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="D18" s="2" t="s">
         <v>64</v>
       </c>
       <c r="E18" s="2" t="s">
@@ -2451,7 +2498,7 @@
       <c r="C19" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D19" s="28" t="s">
+      <c r="D19" s="2" t="s">
         <v>64</v>
       </c>
       <c r="E19" s="2" t="s">
@@ -2489,7 +2536,7 @@
       <c r="C20" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D20" s="28" t="s">
+      <c r="D20" s="2" t="s">
         <v>64</v>
       </c>
       <c r="E20" s="2" t="s">
@@ -2527,7 +2574,7 @@
       <c r="C21" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D21" s="28" t="s">
+      <c r="D21" s="2" t="s">
         <v>64</v>
       </c>
       <c r="E21" s="2" t="s">
@@ -2565,7 +2612,7 @@
       <c r="C22" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D22" s="28" t="s">
+      <c r="D22" s="2" t="s">
         <v>64</v>
       </c>
       <c r="E22" s="2" t="s">
@@ -2603,7 +2650,7 @@
       <c r="C23" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D23" s="28" t="s">
+      <c r="D23" s="2" t="s">
         <v>64</v>
       </c>
       <c r="E23" s="2" t="s">
@@ -4562,7 +4609,9 @@
       <c r="H90" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="I90" s="13"/>
+      <c r="I90" s="37" t="s">
+        <v>423</v>
+      </c>
       <c r="J90" s="13"/>
       <c r="K90" s="19" t="s">
         <v>184</v>
@@ -4671,7 +4720,9 @@
       <c r="I93" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="J93" s="2"/>
+      <c r="J93" s="2" t="s">
+        <v>430</v>
+      </c>
       <c r="K93" s="19" t="s">
         <v>192</v>
       </c>
@@ -4732,7 +4783,9 @@
       <c r="H95" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="I95" s="2"/>
+      <c r="I95" s="36" t="s">
+        <v>421</v>
+      </c>
       <c r="J95" s="2"/>
       <c r="K95" s="19" t="s">
         <v>196</v>
@@ -4766,7 +4819,9 @@
       <c r="H96" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="I96" s="2"/>
+      <c r="I96" s="36" t="s">
+        <v>422</v>
+      </c>
       <c r="J96" s="2"/>
       <c r="K96" s="19" t="s">
         <v>199</v>
@@ -4803,7 +4858,9 @@
       <c r="I97" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="J97" s="2"/>
+      <c r="J97" s="2" t="s">
+        <v>424</v>
+      </c>
       <c r="K97" s="19" t="s">
         <v>202</v>
       </c>
@@ -4903,7 +4960,9 @@
       <c r="I101" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="J101" s="14"/>
+      <c r="J101" s="14" t="s">
+        <v>425</v>
+      </c>
       <c r="K101" s="16" t="s">
         <v>206</v>
       </c>
@@ -5226,7 +5285,7 @@
         <v>143</v>
       </c>
       <c r="J112" s="2"/>
-      <c r="K112" s="29" t="s">
+      <c r="K112" s="28" t="s">
         <v>390</v>
       </c>
       <c r="L112" s="4" t="s">
@@ -5266,7 +5325,7 @@
         <v>37</v>
       </c>
       <c r="J113" s="2"/>
-      <c r="K113" s="29" t="s">
+      <c r="K113" s="28" t="s">
         <v>391</v>
       </c>
       <c r="L113" s="4" t="s">
@@ -5306,7 +5365,7 @@
         <v>299</v>
       </c>
       <c r="J114" s="2"/>
-      <c r="K114" s="29" t="s">
+      <c r="K114" s="28" t="s">
         <v>392</v>
       </c>
       <c r="L114" s="16"/>
@@ -5344,7 +5403,7 @@
         <v>222</v>
       </c>
       <c r="J115" s="15"/>
-      <c r="K115" s="29" t="s">
+      <c r="K115" s="28" t="s">
         <v>393</v>
       </c>
       <c r="L115" s="4" t="s">
@@ -5532,10 +5591,10 @@
       <c r="B123" t="b">
         <v>1</v>
       </c>
-      <c r="C123" s="31" t="s">
+      <c r="C123" s="30" t="s">
         <v>221</v>
       </c>
-      <c r="D123" s="31" t="s">
+      <c r="D123" s="30" t="s">
         <v>171</v>
       </c>
       <c r="E123" s="2" t="s">
@@ -5551,12 +5610,14 @@
       <c r="I123" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="J123" s="2"/>
-      <c r="K123" s="32" t="s">
+      <c r="J123" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="K123" s="31" t="s">
         <v>310</v>
       </c>
       <c r="M123" s="8"/>
-      <c r="N123" s="34" t="s">
+      <c r="N123" s="32" t="s">
         <v>311</v>
       </c>
       <c r="O123" s="2"/>
@@ -5569,10 +5630,10 @@
       <c r="B124" t="b">
         <v>1</v>
       </c>
-      <c r="C124" s="31" t="s">
+      <c r="C124" s="30" t="s">
         <v>221</v>
       </c>
-      <c r="D124" s="31" t="s">
+      <c r="D124" s="30" t="s">
         <v>171</v>
       </c>
       <c r="E124" s="3" t="s">
@@ -5589,11 +5650,11 @@
         <v>415</v>
       </c>
       <c r="J124" s="2"/>
-      <c r="K124" s="32" t="s">
+      <c r="K124" s="31" t="s">
         <v>313</v>
       </c>
       <c r="M124" s="8"/>
-      <c r="N124" s="35" t="s">
+      <c r="N124" s="33" t="s">
         <v>314</v>
       </c>
       <c r="O124" s="2"/>
@@ -5606,10 +5667,10 @@
       <c r="B125" t="b">
         <v>1</v>
       </c>
-      <c r="C125" s="31" t="s">
+      <c r="C125" s="30" t="s">
         <v>221</v>
       </c>
-      <c r="D125" s="31" t="s">
+      <c r="D125" s="30" t="s">
         <v>171</v>
       </c>
       <c r="E125" s="3" t="s">
@@ -5626,11 +5687,11 @@
         <v>416</v>
       </c>
       <c r="J125" s="2"/>
-      <c r="K125" s="32" t="s">
+      <c r="K125" s="31" t="s">
         <v>317</v>
       </c>
       <c r="M125" s="8"/>
-      <c r="N125" s="35" t="s">
+      <c r="N125" s="33" t="s">
         <v>318</v>
       </c>
       <c r="O125" s="2"/>
@@ -5643,10 +5704,10 @@
       <c r="B126" t="b">
         <v>1</v>
       </c>
-      <c r="C126" s="31" t="s">
+      <c r="C126" s="30" t="s">
         <v>221</v>
       </c>
-      <c r="D126" s="31" t="s">
+      <c r="D126" s="30" t="s">
         <v>171</v>
       </c>
       <c r="E126" s="3" t="s">
@@ -5663,11 +5724,11 @@
         <v>417</v>
       </c>
       <c r="J126" s="2"/>
-      <c r="K126" s="32" t="s">
+      <c r="K126" s="31" t="s">
         <v>320</v>
       </c>
       <c r="M126" s="8"/>
-      <c r="N126" s="35" t="s">
+      <c r="N126" s="33" t="s">
         <v>321</v>
       </c>
       <c r="O126" s="2"/>
@@ -5680,10 +5741,10 @@
       <c r="B127" t="b">
         <v>1</v>
       </c>
-      <c r="C127" s="31" t="s">
+      <c r="C127" s="30" t="s">
         <v>221</v>
       </c>
-      <c r="D127" s="31" t="s">
+      <c r="D127" s="30" t="s">
         <v>171</v>
       </c>
       <c r="E127" s="3" t="s">
@@ -5700,11 +5761,11 @@
         <v>418</v>
       </c>
       <c r="J127" s="2"/>
-      <c r="K127" s="32" t="s">
+      <c r="K127" s="31" t="s">
         <v>323</v>
       </c>
       <c r="M127" s="8"/>
-      <c r="N127" s="35" t="s">
+      <c r="N127" s="33" t="s">
         <v>324</v>
       </c>
       <c r="O127" s="2"/>
@@ -5918,8 +5979,10 @@
       <c r="I134" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="J134" s="2"/>
-      <c r="K134" s="29" t="s">
+      <c r="J134" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="K134" s="28" t="s">
         <v>419</v>
       </c>
       <c r="L134" s="16"/>
@@ -6719,11 +6782,11 @@
         <v>143</v>
       </c>
       <c r="J162" s="2"/>
-      <c r="K162" s="30" t="s">
+      <c r="K162" s="29" t="s">
         <v>396</v>
       </c>
       <c r="M162" s="8"/>
-      <c r="N162" s="30" t="s">
+      <c r="N162" s="29" t="s">
         <v>397</v>
       </c>
     </row>
@@ -6756,14 +6819,16 @@
       <c r="I163" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="J163" s="15"/>
-      <c r="K163" s="30" t="s">
+      <c r="J163" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="K163" s="29" t="s">
         <v>400</v>
       </c>
-      <c r="M163" s="30" t="s">
+      <c r="M163" s="29" t="s">
         <v>302</v>
       </c>
-      <c r="N163" s="36" t="s">
+      <c r="N163" s="34" t="s">
         <v>401</v>
       </c>
     </row>
@@ -6791,11 +6856,11 @@
       <c r="H164" s="2"/>
       <c r="I164" s="2"/>
       <c r="J164" s="2"/>
-      <c r="K164" s="30" t="s">
+      <c r="K164" s="29" t="s">
         <v>405</v>
       </c>
       <c r="M164" s="8"/>
-      <c r="N164" s="30" t="s">
+      <c r="N164" s="29" t="s">
         <v>406</v>
       </c>
     </row>
@@ -6826,12 +6891,14 @@
       <c r="I165" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="J165" s="2"/>
-      <c r="K165" s="30" t="s">
+      <c r="J165" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="K165" s="29" t="s">
         <v>409</v>
       </c>
       <c r="M165" s="8"/>
-      <c r="N165" s="37" t="s">
+      <c r="N165" s="35" t="s">
         <v>410</v>
       </c>
     </row>
@@ -6862,19 +6929,21 @@
       <c r="I166" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="J166" s="2"/>
-      <c r="K166" s="29" t="s">
+      <c r="J166" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="K166" s="28" t="s">
         <v>412</v>
       </c>
       <c r="M166" s="8"/>
-      <c r="N166" s="30" t="s">
+      <c r="N166" s="29" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="167" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A167"/>
-      <c r="C167" s="31"/>
-      <c r="D167" s="31"/>
+      <c r="C167" s="30"/>
+      <c r="D167" s="30"/>
       <c r="E167" s="2"/>
       <c r="F167" s="2"/>
       <c r="G167" s="2"/>
@@ -6882,12 +6951,12 @@
       <c r="I167" s="2"/>
       <c r="J167" s="2"/>
       <c r="K167" s="2"/>
-      <c r="L167" s="32"/>
+      <c r="L167" s="31"/>
     </row>
     <row r="168" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A168"/>
-      <c r="C168" s="31"/>
-      <c r="D168" s="31"/>
+      <c r="C168" s="30"/>
+      <c r="D168" s="30"/>
       <c r="E168" s="3"/>
       <c r="F168" s="3"/>
       <c r="G168" s="3"/>
@@ -6895,12 +6964,12 @@
       <c r="I168" s="2"/>
       <c r="J168" s="2"/>
       <c r="K168" s="2"/>
-      <c r="L168" s="32"/>
+      <c r="L168" s="31"/>
     </row>
     <row r="169" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A169"/>
-      <c r="C169" s="31"/>
-      <c r="D169" s="31"/>
+      <c r="C169" s="30"/>
+      <c r="D169" s="30"/>
       <c r="E169" s="3"/>
       <c r="F169" s="3"/>
       <c r="G169" s="3"/>
@@ -6908,12 +6977,12 @@
       <c r="I169" s="2"/>
       <c r="J169" s="2"/>
       <c r="K169" s="2"/>
-      <c r="L169" s="32"/>
+      <c r="L169" s="31"/>
     </row>
     <row r="170" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A170"/>
-      <c r="C170" s="31"/>
-      <c r="D170" s="31"/>
+      <c r="C170" s="30"/>
+      <c r="D170" s="30"/>
       <c r="E170" s="3"/>
       <c r="F170" s="3"/>
       <c r="G170" s="3"/>
@@ -6921,12 +6990,12 @@
       <c r="I170" s="2"/>
       <c r="J170" s="2"/>
       <c r="K170" s="2"/>
-      <c r="L170" s="32"/>
+      <c r="L170" s="31"/>
     </row>
     <row r="171" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A171"/>
-      <c r="C171" s="31"/>
-      <c r="D171" s="31"/>
+      <c r="C171" s="30"/>
+      <c r="D171" s="30"/>
       <c r="E171" s="3"/>
       <c r="F171" s="3"/>
       <c r="G171" s="3"/>
@@ -6934,7 +7003,7 @@
       <c r="I171" s="2"/>
       <c r="J171" s="2"/>
       <c r="K171" s="2"/>
-      <c r="L171" s="32"/>
+      <c r="L171" s="31"/>
     </row>
   </sheetData>
   <hyperlinks>
